--- a/output/checks.xlsx
+++ b/output/checks.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">prolific_id</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t xml:space="preserve">responseid</t>
   </si>
   <si>
     <t xml:space="preserve">pass_video</t>
@@ -23,13 +23,10 @@
     <t xml:space="preserve">pass_attention</t>
   </si>
   <si>
-    <t xml:space="preserve">pass_typing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pass_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pass_ip</t>
+    <t xml:space="preserve">R_3Pw8eqtaKwkReOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R_1gSJxBmH07l3A8u</t>
   </si>
 </sst>
 </file>
@@ -368,19 +365,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -388,73 +376,15 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
